--- a/embeds/data/individual-family-community/slot-14-체류외국인-수와-미등록-체류외국인-비율,-1998-2024.xlsx
+++ b/embeds/data/individual-family-community/slot-14-체류외국인-수와-미등록-체류외국인-비율,-1998-2024.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>장기체류자 수(만 명)</t>
+          <t>장기체류자 수</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1070,7 +1070,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1238,7 +1238,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1322,7 +1322,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1406,7 +1406,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1448,7 +1448,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1532,7 +1532,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>단기체류자 수(만 명)</t>
+          <t>단기체류자 수</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1994,7 +1994,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2036,7 +2036,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>미등록 체류자 비율(%)</t>
+          <t>미등록 체류자 비율</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
